--- a/monthly-bills.xlsx
+++ b/monthly-bills.xlsx
@@ -202,7 +202,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generated 21 Sep 2026 19:56. Per month = twelve-month total / 12.</t>
+          <t xml:space="preserve">Generated 21 Sep 2026 20:19. Per month = twelve-month total / 12.</t>
         </is>
       </c>
     </row>
